--- a/nriss-patch-1/ig/StructureDefinition-fr-cda-vaccinations.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-cda-vaccinations.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:28:18+00:00</t>
+    <t>2026-06-01T15:28:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
